--- a/assets/grade-upload-template.xlsx
+++ b/assets/grade-upload-template.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="작성안내" sheetId="2" r:id="rId2"/>
+    <sheet name="단위수" sheetId="2" r:id="rId2"/>
+    <sheet name="작성안내" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,9 +399,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
@@ -441,32 +442,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>단위수</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -474,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -503,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -532,7 +533,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -561,42 +562,142 @@
         <v>1</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B7"/>
   <cols>
-    <col min="1" max="1" width="58.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>교과</v>
+      </c>
+      <c r="B1" t="str">
+        <v>단위수</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>국어</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>수학</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>영어</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>한국사</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>통합사회</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>통합과학</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A7"/>
+  <cols>
+    <col min="1" max="1" width="62.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -606,27 +707,32 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>① 「Sheet1」 시트에 반·번호·이름과 교과별 원점수를 입력합니다.</v>
+        <v>① Sheet1: 1행 열 제목, 2행 교과별 단위수, 3행부터 학생 성적</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>② 필수 열: 반, 번호, 이름 (학번 열은 넣지 않습니다)</v>
+        <v>② 「단위수」 시트에 교과·단위수만 적어도 인식됩니다 (Sheet1 2행과 동일 역할)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>③ 교과 열: 국어, 수학, 영어, 한국사, 통합사회, 통합과학</v>
+        <v>③ 열 이름을 국어(4) 처럼 적어도 단위수를 인식합니다</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>④ .xlsx로 저장 후 「성적 데이터 등록」에서 업로드합니다.</v>
+        <v>④ 필수: 반·번호·이름 또는 학번·이름 / 교과 열은 학교에 맞게 추가·변경 가능</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>⑤ .xlsx 저장 후 「성적 데이터 등록」에서 업로드</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/assets/grade-upload-template.xlsx
+++ b/assets/grade-upload-template.xlsx
@@ -3,9 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="단위수" sheetId="2" r:id="rId2"/>
-    <sheet name="작성안내" sheetId="3" r:id="rId3"/>
+    <sheet name="정보입력란" sheetId="1" r:id="rId1"/>
+    <sheet name="작성안내" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -624,80 +623,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:A6"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>교과</v>
-      </c>
-      <c r="B1" t="str">
-        <v>단위수</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>국어</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>수학</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>영어</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>한국사</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>통합사회</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>통합과학</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
-  <cols>
-    <col min="1" max="1" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="65.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -707,32 +635,27 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>① Sheet1: 1행 열 제목, 2행 교과별 단위수, 3행부터 학생 성적</v>
+        <v>① 「정보입력란」시트: 1행 열 제목, 2행 과목별 단위수, 3행부터 학생 성적</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>② 「단위수」 시트에 교과·단위수만 적어도 인식됩니다 (Sheet1 2행과 동일 역할)</v>
+        <v>② 단위수는 「정보입력란」 2행(반 열에 「단위수」)에만 적으면 됩니다.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>③ 열 이름을 국어(4) 처럼 적어도 단위수를 인식합니다</v>
+        <v>③ 열 이름을 국어(4)처럼 괄호에 단위수를 넣어도 인식합니다.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>④ 필수: 반·번호·이름 또는 학번·이름 / 교과 열은 학교에 맞게 추가·변경 가능</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>⑤ .xlsx 저장 후 「성적 데이터 등록」에서 업로드</v>
+        <v>④ 필수: 반·번호·이름 또는 학번·이름. .xlsx 저장 후 「성적 데이터 등록」에서 업로드</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
   </ignoredErrors>
 </worksheet>
 </file>